--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,108 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121642452</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90874</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ljungskile - Resterröd, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>317588</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6459085</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>121642452</v>
       </c>
       <c r="B4" t="n">
-        <v>90874</v>
+        <v>90882</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>121642452</v>
       </c>
       <c r="B4" t="n">
-        <v>90882</v>
+        <v>90896</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>121642452</v>
       </c>
       <c r="B4" t="n">
-        <v>90896</v>
+        <v>90898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>121642452</v>
       </c>
       <c r="B4" t="n">
-        <v>90898</v>
+        <v>90899</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,6 +1006,108 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124075141</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58323</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Restenäs 270, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>317495</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6459123</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,6 +1108,107 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129513212</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92002</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Restenäs, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>317556</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6459015</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129513212</v>
       </c>
       <c r="B6" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129513212</v>
       </c>
       <c r="B6" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129513212</v>
       </c>
       <c r="B6" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129513212</v>
       </c>
       <c r="B6" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129513212</v>
       </c>
       <c r="B6" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129513212</v>
       </c>
       <c r="B6" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129513212</v>
       </c>
       <c r="B6" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>129513212</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103816074</v>
+        <v>129513212</v>
       </c>
       <c r="B2" t="n">
-        <v>86314</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4392</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uddevalla, Boh</t>
+          <t>Restenäs, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317537.1157282731</v>
+        <v>317556</v>
       </c>
       <c r="R2" t="n">
-        <v>6459083.780114873</v>
+        <v>6459015</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,6 +757,7 @@
       <c r="AE2" t="b">
         <v>1</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,54 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111787188</v>
+        <v>121642452</v>
       </c>
       <c r="B3" t="n">
-        <v>88915</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5734</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Restenäs 270, Uddevalla, Boh</t>
+          <t>Ljungskile - Resterröd, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>317495</v>
+        <v>317588</v>
       </c>
       <c r="R3" t="n">
-        <v>6459123</v>
+        <v>6459085</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,37 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -906,89 +873,85 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121642452</v>
+        <v>103816074</v>
       </c>
       <c r="B4" t="n">
-        <v>90899</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>4392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ljungskile - Resterröd, Boh</t>
+          <t>Uddevalla, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>317588</v>
+        <v>317537</v>
       </c>
       <c r="R4" t="n">
-        <v>6459085</v>
+        <v>6459084</v>
       </c>
       <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
         <v>1</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Uddevalla</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Resteröd</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1008,40 +971,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124075141</v>
+        <v>124668214</v>
       </c>
       <c r="B5" t="n">
-        <v>58345</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>102980</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Restenäs 270, Uddevalla, Boh</t>
@@ -1078,12 +1050,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,51 +1092,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129513212</v>
+        <v>121474818</v>
       </c>
       <c r="B6" t="n">
-        <v>92052</v>
+        <v>58388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Restenäs, Boh</t>
+          <t>Turebacken, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317556</v>
+        <v>317562</v>
       </c>
       <c r="R6" t="n">
-        <v>6459015</v>
+        <v>6459140</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,21 +1161,25 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stora flockar i trädtopparna.</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,6 +1195,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124075141</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Restenäs 270, Uddevalla, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>317495</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6459123</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29688-2023 artfynd.xlsx
+++ b/artfynd/A 29688-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129513212</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121642452</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103816074</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124668214</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121474818</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,8 +1322,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124075141</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>